--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_67450_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_67450_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R36945926e3914957"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R102510d9862d4365"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,621 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3623</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.3185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.6875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.8653</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.7165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.9930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.6136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.1706</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.0359</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.3999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.6788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7174</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.7371</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.0598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.0436</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.5924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.2427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.0202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.4721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.2327</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.2641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.3964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.7815</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.6101</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.4621</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.6241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3974</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.3551</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3495</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.3398</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.9622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.5242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.7074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.5373</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.9557</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.4419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>04/08/2026</x:t>
         </x:is>
       </x:c>
